--- a/survey_templates/050_laboratory_management_trends_quiz--survey_templates.xlsx
+++ b/survey_templates/050_laboratory_management_trends_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>Your role in laboratory management</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>Your role type in laboratory management</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>key_trends</t>
+          <t>lab_management_trends</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>key_trends</t>
+          <t>What are the key trends in laboratory management?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>What are the key challenges in laboratory management?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>technology_adoption</t>
+          <t>technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>technology_adoption</t>
+          <t>What technologies are being adopted in laboratory management?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>technology_adoption</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_your_role</t>
+          <t>Which technologies are being adopted in laboratory management?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>technology_effectiveness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_is_your_role_type</t>
+          <t>How effective are the technologies in laboratory management?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends</t>
+          <t>What are the benefits of technology adoption in laboratory management?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_challenges</t>
+          <t>challenges_tech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_challenges</t>
+          <t>What are the challenges of technology adoption in laboratory management?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what_are_technologies_being_adopted</t>
+          <t>tech_impact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>what_are_technologies_being_adopted</t>
+          <t>How does technology affect laboratory management?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>What is the future of laboratory management?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>How can laboratory management be improved?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>technology_adoption</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>role_type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laboratory_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laboratory Manager</t>
         </is>
       </c>
     </row>
@@ -1148,828 +849,692 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scientist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scientist</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>technician</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Technician</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>key_trends_choices</t>
+          <t>role_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laboratory_manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laboratory Manager</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>key_trends_choices</t>
+          <t>role_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scientist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scientist</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>role_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>technician</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Technician</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>role_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>lab_management_trends_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>automation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Automation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>lab_management_trends_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>lab_management_trends_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>quality_control</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Quality Control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>lab_management_trends_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>challenges_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>challenges_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>budget_management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Budget Management</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_choices</t>
+          <t>challenges_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>resource_management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Resource Management</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_choices</t>
+          <t>challenges_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_challenges_choices</t>
+          <t>technologies_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laboratory_information_management_systems_(lims)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laboratory Information Management Systems (LIMS)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>what_are_the_key_trends_challenges_choices</t>
+          <t>technologies_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electronic_laboratory_notebooks_(eln)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Electronic Laboratory Notebooks (ELN)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>what_are_technologies_being_adopted_choices</t>
+          <t>technologies_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laboratory_robotics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laboratory Robotics</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>what_are_technologies_being_adopted_choices</t>
+          <t>technologies_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>lims</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>LIMS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>eln</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ELN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laboratory_robotics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laboratory Robotics</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>technology_adoption_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>technology_effectiveness_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>highly_effective</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Highly effective</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>technology_effectiveness_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>technology_effectiveness_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very effective</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>increased_efficiency</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Increased efficiency</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>improved_accuracy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Improved accuracy</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reduced_costs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reduced costs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>challenges_tech_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high_costs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High costs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>challenges_tech_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>limited_accessibility</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Limited accessibility</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>challenges_tech_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>training_requirements</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Training requirements</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>tech_impact_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>positively</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Positively</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>tech_impact_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>negatively</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Negatively</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>technology_adoption_choices</t>
+          <t>tech_impact_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>future_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>increased_automation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Increased automation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>future_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>improved_collaboration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Improved collaboration</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>future_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>enhanced_data_analysis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Enhanced data analysis</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>role_type_choices</t>
+          <t>improvement_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Improved communication</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>improvement_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>enhanced_training</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Enhanced training</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>improvement_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>better_resource_allocation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>technology_adoption_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>technology_adoption_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>role_type_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>role_type_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Better resource allocation</t>
         </is>
       </c>
     </row>
